--- a/FigafJiraIntegration/IntegrationFlow/Search_Jira_Issues/Documentation.xlsx
+++ b/FigafJiraIntegration/IntegrationFlow/Search_Jira_Issues/Documentation.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="105">
   <si>
     <t>Interface Details</t>
   </si>
@@ -302,13 +302,13 @@
     <t>Address</t>
   </si>
   <si>
-    <t>sampledev(cpi-trial-alex)-&gt;sampleqa(cpi-trial-alex)</t>
+    <t>sampledev(trial-cpi-alex)-&gt;sampleqa(trial-cpi-alex)</t>
   </si>
   <si>
     <t>sampledev</t>
   </si>
   <si>
-    <t>/figaf/jira/searchissues</t>
+    <t>/figaf/jira/searchissues3</t>
   </si>
   <si>
     <t>sampleqa</t>
@@ -344,19 +344,19 @@
     <t>ESBMessaging.send</t>
   </si>
   <si>
+    <t>IFlow Configuration</t>
+  </si>
+  <si>
+    <t>Search_Jira_Issues iflow configuration.json</t>
+  </si>
+  <si>
+    <t>2026-07-13 07:12 AM</t>
+  </si>
+  <si>
     <t>Script</t>
   </si>
   <si>
     <t>map_jira_json.groovy</t>
-  </si>
-  <si>
-    <t>2026-07-13 07:12 AM</t>
-  </si>
-  <si>
-    <t>IFlow Configuration</t>
-  </si>
-  <si>
-    <t>Search_Jira_Issues iflow configuration.json</t>
   </si>
 </sst>
 </file>
@@ -2081,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="22.0"/>
@@ -2130,12 +2130,23 @@
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" ht="15.0" customHeight="true">
+      <c r="A7" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B7" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>102</v>
       </c>
     </row>
